--- a/jsgaalop/tests/matrixmuls/resultprepared.xlsx
+++ b/jsgaalop/tests/matrixmuls/resultprepared.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="65">
   <si>
     <t>browser</t>
   </si>
@@ -167,13 +167,55 @@
   </si>
   <si>
     <t>Mflat_ubo</t>
+  </si>
+  <si>
+    <t>Funktion</t>
+  </si>
+  <si>
+    <t>Objekt</t>
+  </si>
+  <si>
+    <t>Old</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>CurveTP</t>
+  </si>
+  <si>
+    <t>DualComplexSummofsquares</t>
+  </si>
+  <si>
+    <t>Pl</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>IntervallSummofsquares</t>
+  </si>
+  <si>
+    <t>DualF</t>
+  </si>
+  <si>
+    <t>Summofsquares</t>
+  </si>
+  <si>
+    <t>xyzDualSummofsquares</t>
+  </si>
+  <si>
+    <t>Alt</t>
+  </si>
+  <si>
+    <t>Neu</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -308,6 +350,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="33">
@@ -651,8 +699,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -890,24 +941,24 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="122745984"/>
-        <c:axId val="122747520"/>
+        <c:axId val="112423680"/>
+        <c:axId val="112425216"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="122745984"/>
+        <c:axId val="112423680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="122747520"/>
+        <c:crossAx val="112425216"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="122747520"/>
+        <c:axId val="112425216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -933,7 +984,7 @@
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="122745984"/>
+        <c:crossAx val="112423680"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -946,7 +997,7 @@
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.70000000000000007" r="0.70000000000000007" t="0.78740157499999996" header="0.30000000000000004" footer="0.30000000000000004"/>
+    <c:pageMargins b="0.78740157499999996" l="0.70000000000000018" r="0.70000000000000018" t="0.78740157499999996" header="0.3000000000000001" footer="0.3000000000000001"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -1331,24 +1382,24 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="142734080"/>
-        <c:axId val="142735616"/>
+        <c:axId val="112464256"/>
+        <c:axId val="112465792"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="142734080"/>
+        <c:axId val="112464256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="142735616"/>
+        <c:crossAx val="112465792"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="142735616"/>
+        <c:axId val="112465792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="200"/>
@@ -1376,7 +1427,7 @@
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="142734080"/>
+        <c:crossAx val="112464256"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1389,7 +1440,7 @@
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.70000000000000007" r="0.70000000000000007" t="0.78740157499999996" header="0.30000000000000004" footer="0.30000000000000004"/>
+    <c:pageMargins b="0.78740157499999996" l="0.70000000000000018" r="0.70000000000000018" t="0.78740157499999996" header="0.3000000000000001" footer="0.3000000000000001"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -1630,24 +1681,24 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="123107584"/>
-        <c:axId val="123113472"/>
+        <c:axId val="112519040"/>
+        <c:axId val="112520576"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="123107584"/>
+        <c:axId val="112519040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="123113472"/>
+        <c:crossAx val="112520576"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="123113472"/>
+        <c:axId val="112520576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1673,7 +1724,7 @@
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="123107584"/>
+        <c:crossAx val="112519040"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1686,7 +1737,7 @@
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.70000000000000007" r="0.70000000000000007" t="0.78740157499999996" header="0.30000000000000004" footer="0.30000000000000004"/>
+    <c:pageMargins b="0.78740157499999996" l="0.70000000000000018" r="0.70000000000000018" t="0.78740157499999996" header="0.3000000000000001" footer="0.3000000000000001"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -2047,24 +2098,24 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="123135488"/>
-        <c:axId val="123137024"/>
+        <c:axId val="128427136"/>
+        <c:axId val="128428672"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="123135488"/>
+        <c:axId val="128427136"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="123137024"/>
+        <c:crossAx val="128428672"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="123137024"/>
+        <c:axId val="128428672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="200"/>
@@ -2092,7 +2143,7 @@
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="123135488"/>
+        <c:crossAx val="128427136"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2105,7 +2156,7 @@
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.70000000000000007" r="0.70000000000000007" t="0.78740157499999996" header="0.30000000000000004" footer="0.30000000000000004"/>
+    <c:pageMargins b="0.78740157499999996" l="0.70000000000000018" r="0.70000000000000018" t="0.78740157499999996" header="0.3000000000000001" footer="0.3000000000000001"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -2310,24 +2361,24 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="143096832"/>
-        <c:axId val="143115008"/>
+        <c:axId val="128449152"/>
+        <c:axId val="128528768"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="143096832"/>
+        <c:axId val="128449152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="143115008"/>
+        <c:crossAx val="128528768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="143115008"/>
+        <c:axId val="128528768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2353,7 +2404,7 @@
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="143096832"/>
+        <c:crossAx val="128449152"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2366,7 +2417,7 @@
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.70000000000000007" r="0.70000000000000007" t="0.78740157499999996" header="0.30000000000000004" footer="0.30000000000000004"/>
+    <c:pageMargins b="0.78740157499999996" l="0.70000000000000018" r="0.70000000000000018" t="0.78740157499999996" header="0.3000000000000001" footer="0.3000000000000001"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -2547,24 +2598,24 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="143144448"/>
-        <c:axId val="143145984"/>
+        <c:axId val="128558208"/>
+        <c:axId val="128559744"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="143144448"/>
+        <c:axId val="128558208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:axPos val="l"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="143145984"/>
+        <c:crossAx val="128559744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="143145984"/>
+        <c:axId val="128559744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2590,7 +2641,7 @@
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="143144448"/>
+        <c:crossAx val="128558208"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2603,7 +2654,776 @@
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.70000000000000007" r="0.70000000000000007" t="0.78740157499999996" header="0.30000000000000004" footer="0.30000000000000004"/>
+    <c:pageMargins b="0.78740157499999996" l="0.70000000000000018" r="0.70000000000000018" t="0.78740157499999996" header="0.3000000000000001" footer="0.3000000000000001"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="de-DE"/>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>resultprepared!$C$74</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Old</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>resultprepared!$A$75:$B$89</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="15"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>CurveTP</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Pl</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>T1</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>CurveTP</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Pl</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>T1</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>CurveTP</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Pl</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>T1</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>CurveTP</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Pl</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>T1</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>CurveTP</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Pl</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>T1</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>DualComplexSummofsquares</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>DualComplexSummofsquares</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>DualComplexSummofsquares</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>IntervallSummofsquares</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>IntervallSummofsquares</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>IntervallSummofsquares</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>DualF</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>DualF</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>DualF</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Summofsquares</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Summofsquares</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Summofsquares</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>xyzDualSummofsquares</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>xyzDualSummofsquares</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>xyzDualSummofsquares</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>resultprepared!$C$75:$C$89</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>176</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36.199999988079</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="General">
+                  <c:v>33.300000011920901</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="General">
+                  <c:v>795.70000004768303</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="General">
+                  <c:v>94.5</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="General">
+                  <c:v>50.899999976158099</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="General">
+                  <c:v>118.399999976158</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="General">
+                  <c:v>31.399999976158099</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="General">
+                  <c:v>22.200000047683702</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="General">
+                  <c:v>113.80000001192001</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="General">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="General">
+                  <c:v>20.600000023841801</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="General">
+                  <c:v>148.5</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="General">
+                  <c:v>24.899999976158099</c:v>
+                </c:pt>
+                <c:pt idx="14" formatCode="General">
+                  <c:v>23.199999988079</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>resultprepared!$D$74</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>New</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>resultprepared!$A$75:$B$89</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="15"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>CurveTP</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Pl</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>T1</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>CurveTP</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Pl</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>T1</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>CurveTP</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Pl</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>T1</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>CurveTP</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Pl</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>T1</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>CurveTP</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Pl</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>T1</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>DualComplexSummofsquares</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>DualComplexSummofsquares</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>DualComplexSummofsquares</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>IntervallSummofsquares</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>IntervallSummofsquares</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>IntervallSummofsquares</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>DualF</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>DualF</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>DualF</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Summofsquares</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Summofsquares</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Summofsquares</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>xyzDualSummofsquares</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>xyzDualSummofsquares</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>xyzDualSummofsquares</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>resultprepared!$D$75:$D$89</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>319.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45.900000035762702</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>32.300000011920901</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400.80000001192002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>32.300000011920901</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24.199999988079</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>124.20000004768301</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12.599999964237201</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>237</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>31.300000011920901</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>17.600000023841801</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:dLbls/>
+        <c:axId val="95044352"/>
+        <c:axId val="95045888"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="95044352"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr rot="0" vert="horz" anchor="ctr" anchorCtr="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="95045888"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="95045888"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="95044352"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="de-DE"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-DE"/>
+              <a:t>Alte gegen Neue Codegenerierung</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.34120783470103827"/>
+          <c:y val="0.16371443569553806"/>
+          <c:w val="0.58248025424075256"/>
+          <c:h val="0.66387911511061115"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>resultprepared!$B$91</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Alt</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>resultprepared!$A$92:$A$106</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>DualComplexSummofsquares CurveTP</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>DualComplexSummofsquares Pl     </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>DualComplexSummofsquares T1     </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>IntervallSummofsquares   CurveTP</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>IntervallSummofsquares   Pl     </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>IntervallSummofsquares   T1     </c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>DualF                    CurveTP</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>DualF                    Pl     </c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>DualF                    T1     </c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Summofsquares            CurveTP</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Summofsquares            Pl     </c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Summofsquares            T1     </c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>xyzDualSummofsquares     CurveTP</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>xyzDualSummofsquares     Pl     </c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>xyzDualSummofsquares     T1     </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>resultprepared!$B$92:$B$106</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0" formatCode="General">
+                  <c:v>176</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36.199999988079</c:v>
+                </c:pt>
+                <c:pt idx="2" formatCode="General">
+                  <c:v>33.300000011920901</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="General">
+                  <c:v>795.70000004768303</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="General">
+                  <c:v>94.5</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="General">
+                  <c:v>50.899999976158099</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="General">
+                  <c:v>118.399999976158</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="General">
+                  <c:v>31.399999976158099</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="General">
+                  <c:v>22.200000047683702</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="General">
+                  <c:v>113.80000001192001</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="General">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="General">
+                  <c:v>20.600000023841801</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="General">
+                  <c:v>148.5</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="General">
+                  <c:v>24.899999976158099</c:v>
+                </c:pt>
+                <c:pt idx="14" formatCode="General">
+                  <c:v>23.199999988079</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>resultprepared!$C$91</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Neu</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>resultprepared!$A$92:$A$106</c:f>
+              <c:strCache>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>DualComplexSummofsquares CurveTP</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>DualComplexSummofsquares Pl     </c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>DualComplexSummofsquares T1     </c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>IntervallSummofsquares   CurveTP</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>IntervallSummofsquares   Pl     </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>IntervallSummofsquares   T1     </c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>DualF                    CurveTP</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>DualF                    Pl     </c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>DualF                    T1     </c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Summofsquares            CurveTP</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Summofsquares            Pl     </c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Summofsquares            T1     </c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>xyzDualSummofsquares     CurveTP</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>xyzDualSummofsquares     Pl     </c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>xyzDualSummofsquares     T1     </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>resultprepared!$C$92:$C$106</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>319.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>45.900000035762702</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>32.300000011920901</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400.80000001192002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>32.300000011920901</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>24.199999988079</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>124.20000004768301</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>16.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12.599999964237201</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>237</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>31.300000011920901</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>17.600000023841801</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="168706048"/>
+        <c:axId val="168707968"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="168706048"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="@" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr rot="0" vert="horz" anchor="t" anchorCtr="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr>
+                <a:latin typeface="Consolas" pitchFamily="49" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="168707968"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="l"/>
+        <c:lblOffset val="100"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="168707968"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="800"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="de-DE"/>
+                  <a:t>ms</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="168706048"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
@@ -2786,6 +3606,66 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>447676</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>123824</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Diagramm 7"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>676274</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Diagramm 8"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3079,10 +3959,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="1" width="41.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.7109375" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -4039,8 +4921,424 @@
         <v>126</v>
       </c>
     </row>
+    <row r="74" spans="1:4">
+      <c r="A74" t="s">
+        <v>51</v>
+      </c>
+      <c r="B74" t="s">
+        <v>52</v>
+      </c>
+      <c r="C74" t="s">
+        <v>53</v>
+      </c>
+      <c r="D74" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B75" t="s">
+        <v>55</v>
+      </c>
+      <c r="C75">
+        <v>176</v>
+      </c>
+      <c r="D75">
+        <v>319.5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" t="s">
+        <v>56</v>
+      </c>
+      <c r="B76" t="s">
+        <v>57</v>
+      </c>
+      <c r="C76" s="2">
+        <v>36.199999988079</v>
+      </c>
+      <c r="D76">
+        <v>45.900000035762702</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" t="s">
+        <v>56</v>
+      </c>
+      <c r="B77" t="s">
+        <v>58</v>
+      </c>
+      <c r="C77">
+        <v>33.300000011920901</v>
+      </c>
+      <c r="D77">
+        <v>32.300000011920901</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" t="s">
+        <v>59</v>
+      </c>
+      <c r="B78" t="s">
+        <v>55</v>
+      </c>
+      <c r="C78">
+        <v>795.70000004768303</v>
+      </c>
+      <c r="D78">
+        <v>400.80000001192002</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" t="s">
+        <v>59</v>
+      </c>
+      <c r="B79" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79">
+        <v>94.5</v>
+      </c>
+      <c r="D79">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" t="s">
+        <v>59</v>
+      </c>
+      <c r="B80" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80">
+        <v>50.899999976158099</v>
+      </c>
+      <c r="D80">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" t="s">
+        <v>60</v>
+      </c>
+      <c r="B81" t="s">
+        <v>55</v>
+      </c>
+      <c r="C81">
+        <v>118.399999976158</v>
+      </c>
+      <c r="D81">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" t="s">
+        <v>60</v>
+      </c>
+      <c r="B82" t="s">
+        <v>57</v>
+      </c>
+      <c r="C82">
+        <v>31.399999976158099</v>
+      </c>
+      <c r="D82">
+        <v>32.300000011920901</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" t="s">
+        <v>60</v>
+      </c>
+      <c r="B83" t="s">
+        <v>58</v>
+      </c>
+      <c r="C83">
+        <v>22.200000047683702</v>
+      </c>
+      <c r="D83">
+        <v>24.199999988079</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" t="s">
+        <v>61</v>
+      </c>
+      <c r="B84" t="s">
+        <v>55</v>
+      </c>
+      <c r="C84">
+        <v>113.80000001192001</v>
+      </c>
+      <c r="D84">
+        <v>124.20000004768301</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" t="s">
+        <v>61</v>
+      </c>
+      <c r="B85" t="s">
+        <v>57</v>
+      </c>
+      <c r="C85">
+        <v>16</v>
+      </c>
+      <c r="D85">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" t="s">
+        <v>61</v>
+      </c>
+      <c r="B86" t="s">
+        <v>58</v>
+      </c>
+      <c r="C86">
+        <v>20.600000023841801</v>
+      </c>
+      <c r="D86">
+        <v>12.599999964237201</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" t="s">
+        <v>62</v>
+      </c>
+      <c r="B87" t="s">
+        <v>55</v>
+      </c>
+      <c r="C87">
+        <v>148.5</v>
+      </c>
+      <c r="D87">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" t="s">
+        <v>62</v>
+      </c>
+      <c r="B88" t="s">
+        <v>57</v>
+      </c>
+      <c r="C88">
+        <v>24.899999976158099</v>
+      </c>
+      <c r="D88">
+        <v>31.300000011920901</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" t="s">
+        <v>62</v>
+      </c>
+      <c r="B89" t="s">
+        <v>58</v>
+      </c>
+      <c r="C89">
+        <v>23.199999988079</v>
+      </c>
+      <c r="D89">
+        <v>17.600000023841801</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="B90" s="1"/>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="B91" t="s">
+        <v>63</v>
+      </c>
+      <c r="C91" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="3" t="str">
+        <f>A75 &amp; REPT(" ", 25- LEN(A75)) &amp; "" &amp; B75 &amp; REPT(" ", 7 - LEN(B75))</f>
+        <v>DualComplexSummofsquares CurveTP</v>
+      </c>
+      <c r="B92">
+        <v>176</v>
+      </c>
+      <c r="C92">
+        <v>319.5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="3" t="str">
+        <f t="shared" ref="A93:A106" si="0">A76 &amp; REPT(" ", 25- LEN(A76)) &amp; "" &amp; B76 &amp; REPT(" ", 7 - LEN(B76))</f>
+        <v xml:space="preserve">DualComplexSummofsquares Pl     </v>
+      </c>
+      <c r="B93" s="2">
+        <v>36.199999988079</v>
+      </c>
+      <c r="C93">
+        <v>45.900000035762702</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">DualComplexSummofsquares T1     </v>
+      </c>
+      <c r="B94">
+        <v>33.300000011920901</v>
+      </c>
+      <c r="C94">
+        <v>32.300000011920901</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>IntervallSummofsquares   CurveTP</v>
+      </c>
+      <c r="B95">
+        <v>795.70000004768303</v>
+      </c>
+      <c r="C95">
+        <v>400.80000001192002</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">IntervallSummofsquares   Pl     </v>
+      </c>
+      <c r="B96">
+        <v>94.5</v>
+      </c>
+      <c r="C96">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">IntervallSummofsquares   T1     </v>
+      </c>
+      <c r="B97">
+        <v>50.899999976158099</v>
+      </c>
+      <c r="C97">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>DualF                    CurveTP</v>
+      </c>
+      <c r="B98">
+        <v>118.399999976158</v>
+      </c>
+      <c r="C98">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">DualF                    Pl     </v>
+      </c>
+      <c r="B99">
+        <v>31.399999976158099</v>
+      </c>
+      <c r="C99">
+        <v>32.300000011920901</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">DualF                    T1     </v>
+      </c>
+      <c r="B100">
+        <v>22.200000047683702</v>
+      </c>
+      <c r="C100">
+        <v>24.199999988079</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>Summofsquares            CurveTP</v>
+      </c>
+      <c r="B101">
+        <v>113.80000001192001</v>
+      </c>
+      <c r="C101">
+        <v>124.20000004768301</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Summofsquares            Pl     </v>
+      </c>
+      <c r="B102">
+        <v>16</v>
+      </c>
+      <c r="C102">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Summofsquares            T1     </v>
+      </c>
+      <c r="B103">
+        <v>20.600000023841801</v>
+      </c>
+      <c r="C103">
+        <v>12.599999964237201</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v>xyzDualSummofsquares     CurveTP</v>
+      </c>
+      <c r="B104">
+        <v>148.5</v>
+      </c>
+      <c r="C104">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">xyzDualSummofsquares     Pl     </v>
+      </c>
+      <c r="B105">
+        <v>24.899999976158099</v>
+      </c>
+      <c r="C105">
+        <v>31.300000011920901</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="3" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">xyzDualSummofsquares     T1     </v>
+      </c>
+      <c r="B106">
+        <v>23.199999988079</v>
+      </c>
+      <c r="C106">
+        <v>17.600000023841801</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>